--- a/data/all_datasets/REDD/REDD_House6_stats/2026-03-27.xlsx
+++ b/data/all_datasets/REDD/REDD_House6_stats/2026-03-27.xlsx
@@ -17927,7 +17927,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -17949,7 +17949,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -19071,7 +19071,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E57" t="n">
